--- a/countries/se-ab/2026-2029.xlsx
+++ b/countries/se-ab/2026-2029.xlsx
@@ -57442,10 +57442,10 @@
         </is>
       </c>
       <c r="N404" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O404" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="U404" t="inlineStr">
         <is>
@@ -65590,7 +65590,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>15249</v>
+        <v>15248</v>
       </c>
     </row>
     <row r="16">

--- a/countries/se-ab/2026-2029.xlsx
+++ b/countries/se-ab/2026-2029.xlsx
@@ -52789,10 +52789,10 @@
         </is>
       </c>
       <c r="N371" t="n">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="O371" t="n">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="U371" t="inlineStr">
         <is>
@@ -65590,7 +65590,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>15248</v>
+        <v>15247</v>
       </c>
     </row>
     <row r="16">
